--- a/config/config_template.xlsx
+++ b/config/config_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shell_tool\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2423C563-80E8-4E29-AF9D-95A2600FCD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DCEFBE-FE3C-4693-8369-57F80CC00C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="364">
   <si>
     <t>SeqNum</t>
   </si>
@@ -263,9 +263,6 @@
     <t>RptList</t>
   </si>
   <si>
-    <t>list</t>
-  </si>
-  <si>
     <t>16.2.1.2</t>
   </si>
   <si>
@@ -396,7 +393,7 @@
   </si>
   <si>
     <t>参与者特征</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>安全性分析</t>
@@ -409,68 +406,7 @@
   </si>
   <si>
     <t>列表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>试验组</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(N=xx)|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对照组</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(N=xx)|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>合计</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(N=xx)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>药物暴露与依从性汇总</t>
@@ -479,9 +415,6 @@
     <t>不良事件AE总结</t>
   </si>
   <si>
-    <t>严重不良事件SAE按SOC和PT降序汇总</t>
-  </si>
-  <si>
     <t>死亡受试者汇总</t>
   </si>
   <si>
@@ -521,9 +454,6 @@
     <t xml:space="preserve">免疫原性结果汇总（受试者层面） </t>
   </si>
   <si>
-    <t xml:space="preserve">抗药抗体（ADA）和/或中和抗体（NAb）检测结果列表 </t>
-  </si>
-  <si>
     <t>筛选情况列表</t>
   </si>
   <si>
@@ -665,426 +595,581 @@
     <t>多次给药后血清中IMM01药代动力学参数汇总</t>
   </si>
   <si>
-    <t>血清中IMM01个体浓度列表</t>
+    <t>ITT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>筛选失败汇总表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有筛选受试者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PKCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PKPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>screen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispositon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rs_base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rs_compare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm_anti</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ae_sum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ae_socpt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PStab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lb_visit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.2.5.5.2</t>
+  </si>
+  <si>
+    <t>抗药抗体（ADA）和/或中和抗体（NAb）检测结果列表</t>
+  </si>
+  <si>
+    <t>scrnlist</t>
+  </si>
+  <si>
+    <t>eotlist</t>
+  </si>
+  <si>
+    <t>eoslist</t>
+  </si>
+  <si>
+    <t>dvlist</t>
+  </si>
+  <si>
+    <t>poplist</t>
+  </si>
+  <si>
+    <t>dmlist</t>
+  </si>
+  <si>
+    <t>mhclist</t>
+  </si>
+  <si>
+    <t>mhnclist</t>
+  </si>
+  <si>
+    <t>cmclist</t>
+  </si>
+  <si>
+    <t>prclist</t>
+  </si>
+  <si>
+    <t>prslist</t>
+  </si>
+  <si>
+    <t>pralist</t>
+  </si>
+  <si>
+    <t>prctlist</t>
+  </si>
+  <si>
+    <t>cmlist</t>
+  </si>
+  <si>
+    <t>prlist</t>
+  </si>
+  <si>
+    <t>prsrlist</t>
+  </si>
+  <si>
+    <t>eximlist</t>
+  </si>
+  <si>
+    <t>extlist</t>
+  </si>
+  <si>
+    <t>exbdlist</t>
+  </si>
+  <si>
+    <t>exgclist</t>
+  </si>
+  <si>
+    <t>pclist</t>
+  </si>
+  <si>
+    <t>pp1list</t>
+  </si>
+  <si>
+    <t>pp2list</t>
+  </si>
+  <si>
+    <t>trtglist</t>
+  </si>
+  <si>
+    <t>oslist</t>
+  </si>
+  <si>
+    <t>fwlist</t>
+  </si>
+  <si>
+    <t>antclist</t>
+  </si>
+  <si>
+    <t>trntlist</t>
+  </si>
+  <si>
+    <t>trnwlist</t>
+  </si>
+  <si>
+    <t>trsplist</t>
+  </si>
+  <si>
+    <t>trbmlist</t>
+  </si>
+  <si>
+    <t>trcplist</t>
+  </si>
+  <si>
+    <t>trptlist</t>
+  </si>
+  <si>
+    <t>rslist</t>
+  </si>
+  <si>
+    <t>pfslist</t>
+  </si>
+  <si>
+    <t>aelist</t>
+  </si>
+  <si>
+    <t>dthlist</t>
+  </si>
+  <si>
+    <t>lblist</t>
+  </si>
+  <si>
+    <t>vslist</t>
+  </si>
+  <si>
+    <t>pelist</t>
+  </si>
+  <si>
+    <t>ecglist</t>
+  </si>
+  <si>
+    <t>ecoglist</t>
+  </si>
+  <si>
+    <t>bmklist</t>
+  </si>
+  <si>
+    <t>adanlist</t>
+  </si>
+  <si>
+    <t>研究日 = 参考日期 – 随机化日期+ 1（如果参考日期为随机化日期或在其之后）或参考日期 – 随机化日期（参考日期在随机化日期之前）</t>
+  </si>
+  <si>
+    <t>意向性治疗(ITT)分析集包括所有随机化入组的受试者。</t>
+  </si>
+  <si>
+    <t>安全性分析集 (SS)包括所有随机化入组且至少接受过一次研究药物治疗的受试者。</t>
+  </si>
+  <si>
+    <t>药代动力学浓度分析集（PKCS）包括至少使用一次试验组研究药物治疗且具有至少一个可评价PK浓度数据的所有受试者。</t>
+  </si>
+  <si>
+    <t>免疫原性分析集（ADAS）包括至少接受一次试验组研究药物治疗，且具有用药前基线和至少一个用药后免疫原性评价数据的受试者。</t>
+  </si>
+  <si>
+    <t>年龄（岁）计算为（知情同意日期-出生日期）/365.25，向下取整。</t>
+  </si>
+  <si>
+    <t>BMI（kg/m 2）= [体重（kg）/（身高 （cm）/100）2]。</t>
+  </si>
+  <si>
+    <t>采用MedDRA XX.X版本进行编码。</t>
+  </si>
+  <si>
+    <t>采用WHODrug XX.X版本进行编码。</t>
+  </si>
+  <si>
+    <t>PK参数计算时，对于BLQ的浓度数据，若出现在第一个可测得浓度之前，将其设定为“0”，若在之后测得，将其设定为“缺失”。</t>
+  </si>
+  <si>
+    <t>无进展生存期(PFS)定义为从随机化日期至首次IRC基于Lugano 2014 评效标准评价为疾病进展或任何原因导致死亡（以先发生者为准）日期之间的时间。PFS时间（月）计算为（首次PD或死亡/删失日期-随机化日期 + 1）/30.4375。</t>
+  </si>
+  <si>
+    <t>缓解持续时间（DoR）定义为从首次记录CR或PR证据至第一次评估为疾病进展或发生全因死亡（以先发生者为准）的时间。</t>
+  </si>
+  <si>
+    <t>总生存期（OS）定义为从随机化开始到由任何原因导致死亡的时间。</t>
+  </si>
+  <si>
+    <t>随访时间定义为从首次给药日至死亡日期的时间；若受试者仍存活，则截止至数据库锁库日期；若受试者已退出试验（包括失访），则截止至数据库截止日期前最后一次已知存活日期。</t>
+  </si>
+  <si>
+    <t>治疗期不良事件(TEAE)，定义为研究治疗首次给药后发生或恶化的AE。</t>
+  </si>
+  <si>
+    <t>根据NCI-CTCAE版本5.0对AE的严重程度进行分级。</t>
+  </si>
+  <si>
+    <t>严重不良事件标准：A=导致死亡，B=危及生命，C=导致住院或延长住院事件，D=导致永久性或明显残疾或器官功能损伤，E=导致先天畸形或出生缺陷，F=其他重要医学事件。</t>
+  </si>
+  <si>
+    <t>采用首次给予研究药物前或随机化日期前的末次非缺失测量/评估作为基线。</t>
+  </si>
+  <si>
+    <t>根据NCI-CTCAE版本5.0进行分级。</t>
+  </si>
+  <si>
+    <t>列表 16.2.1.1, 16.2.1.2,16.2.1.3</t>
+  </si>
+  <si>
+    <t>全分析集(FAS)包括所有随机化入组且至少接受过一次研究药物治疗的受试者。对于基于FAS的分析，受试者分组将以随机化分配的治疗为准。</t>
+  </si>
+  <si>
+    <t>安全性分析集 (SS)包括所有随机化入组且至少接受过一次研究药物治疗的受试者。对于基于SS的分析，受试者分组将以实际接受治疗的分组为准。</t>
+  </si>
+  <si>
+    <t>列表 16.2.3</t>
+  </si>
+  <si>
+    <t>列表 16.2.2</t>
+  </si>
+  <si>
+    <t>列表 16.2.4.1</t>
+  </si>
+  <si>
+    <t>列表 16.2.4.2</t>
+  </si>
+  <si>
+    <t>同一受试者在每个SOC和PT下只被计数一次，并按试验组降序显示。</t>
+  </si>
+  <si>
+    <t>列表 16.2.4.3</t>
+  </si>
+  <si>
+    <t>*按受试者最大治疗线数汇总。</t>
+  </si>
+  <si>
+    <t>列表 16.2.4.4.1</t>
+  </si>
+  <si>
+    <t>列表 16.2.4.4.2, 16.2.4.4.3, 16.2.4.4.4, 16.2.4.4.5</t>
+  </si>
+  <si>
+    <t>每名受试者在每个ATC 3级别和首选名称类别中仅计数一次，并按试验组降序显示。若该药物不能编码至ATC3级别，则该药物的最终可编码级别将参与汇总。</t>
+  </si>
+  <si>
+    <t>合并用药/操作定义为在初次给药日期当天或之后正在进行或已结束的任何用药/操作。</t>
+  </si>
+  <si>
+    <t>列表 16.2.4.5.1</t>
+  </si>
+  <si>
+    <t>替雷利珠单抗：暴露持续时间 (月)=(末次给药日期-首次给药日期 + 21)/ 30.4375；暴露持续周期(周期)= 暴露持续时间(天)/21；总累积剂量(mg)= 受试者接受的替雷利珠单抗剂量(mg)之和；实际剂量强度(mg/3周)= 总累积剂量(mg)/ [ (末次给药日期-首次给药日期 + 21)/21]；相对剂量强度(%)=实际剂量强度/计划剂量强度*100%，其中计划剂量强度为200mg每3周</t>
+  </si>
+  <si>
+    <t>注射用IMM01：暴露持续时间 (月)=(末次给药日期-首次给药日期 + 7)/ 30.4375;暴露持续周期(周期)=暴露持续时间(天)/21;总累积剂量(mg)= 受试者接受的IMM01剂量(mg)之和;总校准累积剂量(mg/kg)= 总累积剂量(mg)/ 体重(kg);实际剂量强度(mg/kg/周)= 总校准累积剂量(mg/kg) /  (末次给药日期-首次给药日期 + 7)/7;相对剂量强度(%)=实际剂量强度/计划剂量强度*100%，其中计划剂量强度为2.0 mg/kg每周</t>
+  </si>
+  <si>
+    <t>苯达莫司汀：暴露持续时间 (月)= (末次给药日期-首次给药日期 +28)/ 30.4375, 若末次给药为本周期的第1天给药；或(末次给药日期-首次给药日期 +27)/ 30.4375，若末次给药为本周期的第2天给药. 暴露持续周期(周期)=暴露持续时间(天)/28;总累积剂量(mg)= 受试者接受的苯达莫司汀剂量(mg)之和;总校准累积剂量(mg/m2)=总累积剂量(mg)/BSA(m2),其中BSA(m2) = 0.0061×身高(cm) + 0.0124×体重(kg) - 0.0099.实际剂量强度(mg/m2/4周)= 总校准累积剂量(mg/m2)/ 暴露持续周期;相对剂量强度(%)=实际剂量强度/计划剂量强度*100%，其中计划剂量强度每次为90 mg/m2或者120mg/m2，每4周为一个周期，具体结合受试者耐受程度和研究中心实践选择起始给药剂量。则一个周期的计划剂量强度为180 mg/m2/4周或者240mg/m2/4周</t>
+  </si>
+  <si>
+    <t>吉西他滨：暴露持续时间 (月)= (末次给药日期-首次给药日期 +7   )/ 30.4375, 若末次给药为本周期的第1天给药；或(末次给药日期-首次给药日期 +14)/ 30.4375，若末次给药为本周期的第8天给药.暴露持续周期(周期)= 暴露持续时间(天)/21;总累积剂量(mg)= 受试者接受的吉西他滨剂量(mg)之和;总校准累积剂量(mg/m2)=总累积剂量(mg)/BSA(m2),其中BSA(m2) = 0.0061×身高(cm) + 0.0124×体重(kg) - 0.0099.实际剂量强度(mg/m2/3周)= 总校准累积剂量(mg/m2)/暴露持续周期;相对剂量强度(%)=实际剂量强度/计划剂量强度*100%，其中计划剂量强度2000 mg/m2每3周 （1000 mg/m2每3周为一个治疗周期，每个周期的第1天和第8天给药一次）</t>
+  </si>
+  <si>
+    <t>依从性(%)=实际给药剂量(mg)之和/计划给药剂量(mg)之和</t>
+  </si>
+  <si>
+    <t>列表 16.2.5.1, 16.2.5.2, 16.2.5.3, 16.2.5.4</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>图</t>
+  </si>
+  <si>
+    <t>14.2.2.1.1.2</t>
+  </si>
+  <si>
+    <t>IRC基于2014 Lugano淋巴瘤疗效评价标准评估的无进展生存期（PFS）Kaplan-Meier曲线图</t>
+  </si>
+  <si>
+    <t>ITT</t>
+  </si>
+  <si>
+    <t>列表 16.2.6.9.1</t>
+  </si>
+  <si>
+    <t>14.2.2.1.5.2</t>
+  </si>
+  <si>
+    <t>IRC基于2014 Lugano淋巴瘤疗效评价标准评估的无进展生存期（PFS）Cox比例风险模型估计：森林图</t>
+  </si>
+  <si>
+    <t>使用分层Cox比例风险模型（分层同主要分析相同；若分层因素同该亚组相同，则不使用该分层因素），估计风险比HR及其双侧95%CI。</t>
+  </si>
+  <si>
+    <t>14.2.4.1.2</t>
+  </si>
+  <si>
+    <t>IRC基于2014 Lugano淋巴瘤疗效评价标准评估的个体肿瘤缓解-治疗时间泳道图</t>
+  </si>
+  <si>
+    <t>最佳总体疗效达到客观缓解的受试者</t>
+  </si>
+  <si>
+    <t>列表 16.2.6.8.1</t>
+  </si>
+  <si>
+    <t>列表 16.2.6.1.1, 16.2.6.2.1, 16.2.6.3.1, 16.2.6.4.1, 16.2.6.7.1</t>
+  </si>
+  <si>
+    <t>采用分层对数秩检验（stratified log-rank test），按照随机化的分层因素：包括是否接受过干细胞移植（是或否）和ECOG评分（0/1 或2）（如适用），对PFS进行组间差异检验。</t>
+  </si>
+  <si>
+    <t>使用分层Cox比例风险模型（使用Efron结点处理法），按照随机化的分层因素：包括是否接受过干细胞移植（是或否）和ECOG评分（0/1 或2）（如适用），估计风险比HR及其双侧95%CI。</t>
+  </si>
+  <si>
+    <t>使用Kaplan-Meier（KM）方法估计各治疗组的中位时间，根据Brookmeyer和Crowley方法计算中位生存时间的95%CI。生存率的95%CI的计算基于Greenwood公式计算的标准误的Log-Log转换。</t>
+  </si>
+  <si>
+    <t>风险比为试验组：对照组，风险比&lt;1，说明IMM01联合替雷利珠单抗试验组优于苯达莫司汀或吉西他滨化疗对照组。</t>
+  </si>
+  <si>
+    <t>Programming Note: 对于DOR分析，Kaplan-Meier 统计量需额外报告最大值和最小值；敏感性分析的删失汇总项与主分析有区别。</t>
+  </si>
+  <si>
+    <t>列表 16.2.6.11</t>
+  </si>
+  <si>
+    <t>最佳总体疗效（BOR）定义为基于Lugano2014疗效评价标准进行的所有总体疗效评估中的最佳疗效（CR优于PR优于SD）。</t>
+  </si>
+  <si>
+    <t>客观缓解率（ORR）定义为达到部分缓解（PR）或完全缓解（CR）的受试者比例。完全缓解率（CRR）定义为达到CR的受试者比例。</t>
+  </si>
+  <si>
+    <t>使用分层Miettinen和Nurminen方法按照随机化的分层因素：包括是否接受过干细胞移植（是或否）和ECOG评分（0/1 或2）（如适用），进行组间差异的检验，并报告组间差异的估计及其95%CI。同时，使用双侧95%Clopper-Pearson CI总结每组的ORR和CRR 。</t>
+  </si>
+  <si>
+    <t>列表 16.2.6.8.1, 16.2.6.8.2</t>
+  </si>
+  <si>
+    <t>列表 16.2.6.12</t>
+  </si>
+  <si>
+    <t>对于低于定量下限（BLQ）的浓度数据，设定为“0”。</t>
+  </si>
+  <si>
+    <t>浓度单位：单位</t>
+  </si>
+  <si>
+    <t>EOI: 给药结束后即刻</t>
+  </si>
+  <si>
+    <t>列表 16.2.5.5.1</t>
+  </si>
+  <si>
+    <t>列表 16.2.5.5.2</t>
+  </si>
+  <si>
+    <t>列表 16.2.5.5.3</t>
+  </si>
+  <si>
+    <t>根据NCI-CTCAE版本5.0对AE的严重程度进行分级。缺失严重程度的AE将被视为3级。</t>
+  </si>
+  <si>
+    <t>与研究药物关系记录为“肯定有关”、 “很可能有关”和 “可能有关”的TEAE被视为药物相关。与研究药物关系缺失的TEAE将被视为与研究药物“相关”。</t>
+  </si>
+  <si>
+    <t>如果受试者的同一AE报告次数不止一次，则仅对该受试者只计 最高严重程度/毒性/与研究药物相关性最强 的一条；在例次计算中记录为多条。</t>
+  </si>
+  <si>
+    <t>对于治疗组的受试者，与研究药物相关的AE为与IMM01或与替雷利珠单抗相关的AE；导致暂停用药的AE为导致IMM01或替雷利珠单抗暂停用药的AE；导致剂量降低的AE为导致IMM01或替雷利珠单抗剂量降低的AE；导致研究药物停用的AE为导致IMM01或替雷利珠单抗永久停用的AE。</t>
+  </si>
+  <si>
+    <t>*E代表例次</t>
+  </si>
+  <si>
+    <t>列表 16.2.7.1</t>
+  </si>
+  <si>
+    <t>将根据NCI-CTCAE版本5.0对AE的严重程度进行分级。缺失严重程度的AE将被视为3级  。</t>
+  </si>
+  <si>
+    <t>如果受试者的同一AE报告次数不止一次，则仅对该受试者只计最高严重程度/毒性/与研究药物相关性最强的一条。</t>
+  </si>
+  <si>
+    <t>列表 16.2.7.2</t>
+  </si>
+  <si>
+    <t>列表 16.2.7.6</t>
+  </si>
+  <si>
+    <t>列表 16.2.8.1</t>
+  </si>
+  <si>
+    <t>列表 16.2.8.6</t>
+  </si>
+  <si>
+    <t>列表 16.2.8.8</t>
+  </si>
+  <si>
+    <t>ADA阳性（治疗期间ADA阳性）：包括治疗增强ADA阳性和治疗诱导ADA阳性的所有受试者。ADA阴性：非ADA阳性的受试者将被归类为ADA阴性。</t>
+  </si>
+  <si>
+    <t>NAb阳性：ADA阳性受试者中，有一个或以上 NAb样本检测结果为阳性的受试者。Nab阴性：ADA阴性的受试者或者ADA阳性受试者中Nab阴性的受试者。</t>
+  </si>
+  <si>
+    <t>试验组(N=xx)|对照组(N=xx)|合计(N=xx)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEAE按SOC和PT汇总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAE按SOC和PT汇总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血常规各指标检查结果和相对基线变化情况 - 按访视汇总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血常规各指标检查结果 - 基线与基线后最高CTCAE分级的交叉表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尿常规各指标检查结果情况 - 按访视汇总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尿常规各指标检查结果情况 - 基线与基线后最差临床意义结果的交叉表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECOG评分结果 - 按访视汇总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">免疫原性结果-按访视汇总 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">血清中IMM01个体浓度列表 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">首次给药后血清中IMM01药代动力学参数（含诊断参数）列表 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>多次给药后血清中IMM01药代动力学参数（含诊断参数）列表</t>
-  </si>
-  <si>
-    <t>ITT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>筛选失败汇总表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有筛选受试者</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PKCS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PKPS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IMS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>screen</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dispositon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>set</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pd</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>demo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>diag</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>mh</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmh</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pr</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cm</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rs_base</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pfs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fw</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rs_compare</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cm_anti</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pk</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ae_sum</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ae_socpt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>TEAE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>SOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>PT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>汇总</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dd</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PStab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>lb_visit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>血常规各指标检查结果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>基线与基线后最高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>CTCAE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>分级的交叉表</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>血常规各指标检查结果和相对基线变化情况</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按访视汇总</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>尿常规各指标检查结果情况</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按访视汇总</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>尿常规各指标检查结果情况</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>基线与基线后最差临床意义结果的交叉表</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ECOG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>评分结果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按访视汇总</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>免疫原性结果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按访视汇总</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1102,23 +1187,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1129,10 +1201,36 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1143,20 +1241,20 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1454,30 +1552,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z75"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z79"/>
+  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="83.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="64.5703125" customWidth="1"/>
-    <col min="11" max="11" width="68.7109375" customWidth="1"/>
-    <col min="12" max="13" width="6.7109375" customWidth="1"/>
-    <col min="14" max="14" width="48.7109375" customWidth="1"/>
-    <col min="15" max="21" width="9.7109375" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" customWidth="1"/>
-    <col min="23" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" customWidth="1"/>
-    <col min="26" max="26" width="11.7109375" customWidth="1"/>
+    <col min="1" max="16384" width="16.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1557,15 +1638,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>14.1</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>123</v>
+      <c r="C2" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>27</v>
@@ -1573,20 +1654,20 @@
       <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>198</v>
+      <c r="F2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>129</v>
+        <v>197</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>29</v>
@@ -1600,52 +1681,30 @@
       <c r="N2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
       <c r="Z2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>14.1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>123</v>
+      <c r="C3" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>27</v>
@@ -1653,20 +1712,20 @@
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>152</v>
+      <c r="F3" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>129</v>
+        <v>198</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>29</v>
@@ -1680,52 +1739,30 @@
       <c r="N3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
       <c r="Z3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>14.1</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>123</v>
+      <c r="C4" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>27</v>
@@ -1734,19 +1771,19 @@
         <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>129</v>
+        <v>199</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>29</v>
@@ -1761,51 +1798,39 @@
         <v>29</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>29</v>
+        <v>267</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>29</v>
+        <v>286</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>29</v>
+        <v>287</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>29</v>
+        <v>269</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
       <c r="Z4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>14.1</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>123</v>
+      <c r="C5" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>27</v>
@@ -1814,19 +1839,19 @@
         <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>29</v>
@@ -1840,52 +1865,30 @@
       <c r="N5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
       <c r="Z5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>14.1</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>123</v>
+      <c r="C6" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>27</v>
@@ -1894,19 +1897,19 @@
         <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>129</v>
+        <v>201</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>29</v>
@@ -1921,51 +1924,33 @@
         <v>29</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
       <c r="Z6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>14.1</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>123</v>
+      <c r="C7" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>27</v>
@@ -1974,19 +1959,19 @@
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>129</v>
+        <v>202</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>29</v>
@@ -2000,52 +1985,30 @@
       <c r="N7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
       <c r="Z7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>14.1</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>123</v>
+      <c r="C8" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>27</v>
@@ -2054,19 +2017,19 @@
         <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>129</v>
+        <v>203</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>29</v>
@@ -2081,51 +2044,33 @@
         <v>29</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>29</v>
+        <v>273</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
       <c r="Z8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>14.1</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>123</v>
+      <c r="C9" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>27</v>
@@ -2134,19 +2079,19 @@
         <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>129</v>
+        <v>204</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>29</v>
@@ -2161,51 +2106,31 @@
         <v>29</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
       <c r="Z9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>14.1</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>123</v>
+      <c r="C10" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>27</v>
@@ -2214,19 +2139,19 @@
         <v>37</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>129</v>
+        <v>205</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>29</v>
@@ -2240,52 +2165,30 @@
       <c r="N10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
       <c r="Z10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>14.1</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>123</v>
+      <c r="C11" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>27</v>
@@ -2294,19 +2197,19 @@
         <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>129</v>
+        <v>206</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>29</v>
@@ -2321,51 +2224,35 @@
         <v>29</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>29</v>
+        <v>274</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>29</v>
+        <v>297</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
       <c r="Z11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>14.3</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>125</v>
+        <v>14.1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>27</v>
@@ -2374,19 +2261,19 @@
         <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>129</v>
+        <v>207</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>40</v>
@@ -2401,51 +2288,39 @@
         <v>29</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>29</v>
+        <v>300</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>29</v>
+        <v>301</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>29</v>
+        <v>302</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>29</v>
+        <v>303</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
       <c r="Z12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>14.2</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>126</v>
+      <c r="C13" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>27</v>
@@ -2454,19 +2329,19 @@
         <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>129</v>
+        <v>208</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>42</v>
@@ -2480,52 +2355,30 @@
       <c r="N13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
       <c r="Z13" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>14.2</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>126</v>
+      <c r="C14" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>27</v>
@@ -2534,19 +2387,19 @@
         <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>129</v>
+        <v>209</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>29</v>
@@ -2561,235 +2414,159 @@
         <v>29</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>29</v>
+        <v>321</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>29</v>
+        <v>322</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
       <c r="Z14" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>126</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>27</v>
+        <v>307</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>308</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>45</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
       <c r="O15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
       <c r="Z15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>126</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>307</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>312</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
       <c r="O16" s="1" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
       <c r="Z16" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1">
         <v>14.2</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>126</v>
+      <c r="C17" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>129</v>
+        <v>210</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>29</v>
@@ -2798,78 +2575,58 @@
         <v>29</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
       <c r="Z17" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1">
-        <v>14.1</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>14.2</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>129</v>
+        <v>211</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>29</v>
@@ -2881,155 +2638,103 @@
         <v>29</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>29</v>
+        <v>326</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>29</v>
+        <v>327</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
       <c r="Z18" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1">
-        <v>14.3</v>
-      </c>
-      <c r="C19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>307</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>191</v>
+        <v>316</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
       <c r="Z19" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1">
-        <v>14.3</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>14.2</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>129</v>
+        <v>212</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>29</v>
@@ -3040,73 +2745,51 @@
       <c r="N20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
       <c r="Z20" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1">
-        <v>14.3</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>125</v>
+        <v>14.1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>193</v>
+        <v>51</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>129</v>
+        <v>213</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>29</v>
@@ -3120,76 +2803,54 @@
       <c r="N21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
       <c r="Z21" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1">
         <v>14.3</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>125</v>
+      <c r="C22" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>129</v>
+        <v>214</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>29</v>
@@ -3201,75 +2862,59 @@
         <v>29</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>29</v>
+        <v>331</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>29</v>
+        <v>332</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
       <c r="Z22" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1">
         <v>14.3</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>125</v>
+      <c r="C23" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>129</v>
+        <v>214</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>29</v>
@@ -3278,73 +2923,55 @@
         <v>29</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
       <c r="Z23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B24" s="1">
         <v>14.3</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>125</v>
+      <c r="C24" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>132</v>
+        <v>55</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>29</v>
@@ -3359,72 +2986,52 @@
         <v>29</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
       <c r="Z24" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1">
         <v>14.3</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>125</v>
+      <c r="C25" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>129</v>
+        <v>215</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>29</v>
@@ -3439,75 +3046,65 @@
         <v>29</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>29</v>
+        <v>280</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>29</v>
+        <v>337</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>29</v>
+        <v>338</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>29</v>
+        <v>339</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>29</v>
+        <v>340</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
       <c r="Z25" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B26" s="1">
         <v>14.3</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>125</v>
+      <c r="C26" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>228</v>
+        <v>57</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>225</v>
+        <v>28</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>129</v>
+        <v>216</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>29</v>
@@ -3519,75 +3116,61 @@
         <v>29</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>29</v>
+        <v>273</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>29</v>
+        <v>280</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>29</v>
+        <v>343</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
       <c r="Z26" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1">
         <v>14.3</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>125</v>
+      <c r="C27" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>227</v>
+        <v>59</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>129</v>
+        <v>218</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>29</v>
@@ -3598,73 +3181,49 @@
       <c r="N27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O27" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1">
         <v>14.3</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>125</v>
+      <c r="C28" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>229</v>
+        <v>60</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>129</v>
+        <v>217</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>29</v>
@@ -3678,76 +3237,43 @@
       <c r="N28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Z28" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1">
         <v>14.3</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>125</v>
+      <c r="C29" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>230</v>
+        <v>61</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>28</v>
+        <v>218</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>29</v>
@@ -3758,76 +3284,46 @@
       <c r="N29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z29" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B30" s="1">
         <v>14.3</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>125</v>
+      <c r="C30" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>231</v>
+        <v>356</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>129</v>
+        <v>64</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>29</v>
@@ -3838,73 +3334,46 @@
       <c r="N30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O30" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>127</v>
+        <v>14.3</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>232</v>
+        <v>66</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>129</v>
+        <v>67</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>29</v>
@@ -3918,76 +3387,46 @@
       <c r="N31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O31" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>127</v>
+        <v>14.3</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>145</v>
+        <v>358</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>129</v>
+        <v>69</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>29</v>
@@ -3998,73 +3437,43 @@
       <c r="N32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z32" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1">
-        <v>16.2</v>
+        <v>14.3</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>198</v>
+        <v>71</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>129</v>
+        <v>72</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>29</v>
@@ -4078,73 +3487,40 @@
       <c r="N33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z33" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Z33" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1">
-        <v>16.2</v>
+        <v>14.5</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>149</v>
+        <v>73</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>196</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>129</v>
+        <v>74</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>29</v>
@@ -4158,73 +3534,40 @@
       <c r="N34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z34" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Z34" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B35" s="1">
-        <v>16.2</v>
+        <v>14.5</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>196</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>129</v>
+        <v>76</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>29</v>
@@ -4238,73 +3581,46 @@
       <c r="N35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z35" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O35" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1">
         <v>16.2</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>128</v>
+      <c r="C36" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>83</v>
+      <c r="E36" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>129</v>
+      <c r="I36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>29</v>
@@ -4318,26 +3634,8 @@
       <c r="N36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>29</v>
+      <c r="O36" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>29</v>
@@ -4355,36 +3653,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B37" s="1">
         <v>16.2</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>128</v>
+      <c r="C37" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>151</v>
+      <c r="E37" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>129</v>
+      <c r="I37" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>29</v>
@@ -4398,26 +3696,8 @@
       <c r="N37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>29</v>
+      <c r="O37" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>29</v>
@@ -4435,36 +3715,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B38" s="1">
         <v>16.2</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>128</v>
+      <c r="C38" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>85</v>
+      <c r="E38" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>129</v>
+      <c r="I38" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>29</v>
@@ -4478,26 +3758,8 @@
       <c r="N38" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>29</v>
+      <c r="O38" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>29</v>
@@ -4515,36 +3777,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1">
         <v>16.2</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>128</v>
+      <c r="C39" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>168</v>
+      <c r="E39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>129</v>
+      <c r="I39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>29</v>
@@ -4558,26 +3820,8 @@
       <c r="N39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>29</v>
+      <c r="O39" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V39" s="1" t="s">
         <v>29</v>
@@ -4595,36 +3839,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1">
         <v>16.2</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>128</v>
+      <c r="C40" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>169</v>
+      <c r="E40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>129</v>
+      <c r="I40" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>29</v>
@@ -4638,26 +3882,17 @@
       <c r="N40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>29</v>
+      <c r="O40" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>29</v>
@@ -4675,36 +3910,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B41" s="1">
         <v>16.2</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>128</v>
+      <c r="C41" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>170</v>
+      <c r="E41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>129</v>
+      <c r="I41" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>29</v>
@@ -4718,26 +3953,11 @@
       <c r="N41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>29</v>
+      <c r="O41" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="V41" s="1" t="s">
         <v>29</v>
@@ -4755,36 +3975,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B42" s="1">
         <v>16.2</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>128</v>
+      <c r="C42" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>171</v>
+      <c r="E42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>129</v>
+      <c r="I42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>29</v>
@@ -4798,26 +4018,8 @@
       <c r="N42" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>29</v>
+      <c r="O42" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V42" s="1" t="s">
         <v>29</v>
@@ -4835,36 +4037,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1">
         <v>16.2</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>128</v>
+      <c r="C43" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>172</v>
+      <c r="E43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>129</v>
+      <c r="I43" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>29</v>
@@ -4878,26 +4080,11 @@
       <c r="N43" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>29</v>
+      <c r="O43" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>29</v>
@@ -4915,36 +4102,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B44" s="1">
         <v>16.2</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>128</v>
+      <c r="C44" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>173</v>
+      <c r="E44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>129</v>
+      <c r="I44" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>29</v>
@@ -4958,26 +4145,11 @@
       <c r="N44" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>29</v>
+      <c r="O44" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>29</v>
@@ -4995,36 +4167,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B45" s="1">
         <v>16.2</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>128</v>
+      <c r="C45" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>174</v>
+      <c r="E45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>129</v>
+      <c r="I45" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>29</v>
@@ -5038,26 +4210,8 @@
       <c r="N45" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>29</v>
+      <c r="O45" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>29</v>
@@ -5075,36 +4229,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B46" s="1">
         <v>16.2</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>128</v>
+      <c r="C46" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>175</v>
+      <c r="E46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>129</v>
+      <c r="I46" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>29</v>
@@ -5118,26 +4272,11 @@
       <c r="N46" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>29</v>
+      <c r="O46" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="V46" s="1" t="s">
         <v>29</v>
@@ -5155,36 +4294,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B47" s="1">
         <v>16.2</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>128</v>
+      <c r="C47" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>176</v>
+      <c r="E47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>129</v>
+      <c r="I47" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>29</v>
@@ -5198,26 +4337,8 @@
       <c r="N47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>29</v>
+      <c r="O47" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V47" s="1" t="s">
         <v>29</v>
@@ -5235,36 +4356,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B48" s="1">
         <v>16.2</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>128</v>
+      <c r="C48" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>177</v>
+      <c r="E48" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>129</v>
+      <c r="I48" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>29</v>
@@ -5278,26 +4399,8 @@
       <c r="N48" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U48" s="1" t="s">
-        <v>29</v>
+      <c r="O48" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>29</v>
@@ -5315,36 +4418,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B49" s="1">
         <v>16.2</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>128</v>
+      <c r="C49" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>134</v>
+      <c r="E49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>129</v>
+      <c r="I49" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>29</v>
@@ -5358,26 +4461,11 @@
       <c r="N49" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O49" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S49" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T49" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U49" s="1" t="s">
-        <v>29</v>
+      <c r="O49" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="V49" s="1" t="s">
         <v>29</v>
@@ -5395,36 +4483,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B50" s="1">
         <v>16.2</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>128</v>
+      <c r="C50" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>135</v>
+      <c r="E50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>129</v>
+      <c r="I50" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>29</v>
@@ -5438,26 +4526,11 @@
       <c r="N50" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U50" s="1" t="s">
-        <v>29</v>
+      <c r="O50" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="V50" s="1" t="s">
         <v>29</v>
@@ -5475,36 +4548,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B51" s="1">
         <v>16.2</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>128</v>
+      <c r="C51" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>136</v>
+      <c r="E51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>129</v>
+      <c r="I51" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>29</v>
@@ -5518,26 +4591,11 @@
       <c r="N51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>29</v>
+      <c r="O51" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="V51" s="1" t="s">
         <v>29</v>
@@ -5555,36 +4613,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B52" s="1">
         <v>16.2</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>128</v>
+      <c r="C52" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>137</v>
+      <c r="E52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>129</v>
+      <c r="I52" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>29</v>
@@ -5598,26 +4656,8 @@
       <c r="N52" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>29</v>
+      <c r="O52" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V52" s="1" t="s">
         <v>29</v>
@@ -5635,36 +4675,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B53" s="1">
         <v>16.2</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>128</v>
+      <c r="C53" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>194</v>
+      <c r="E53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>129</v>
+      <c r="I53" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>29</v>
@@ -5678,26 +4718,8 @@
       <c r="N53" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>29</v>
+      <c r="O53" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V53" s="1" t="s">
         <v>29</v>
@@ -5715,36 +4737,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B54" s="1">
         <v>16.2</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>128</v>
+      <c r="C54" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>101</v>
+      <c r="E54" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>129</v>
+      <c r="I54" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>29</v>
@@ -5758,26 +4780,8 @@
       <c r="N54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>29</v>
+      <c r="O54" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V54" s="1" t="s">
         <v>29</v>
@@ -5795,36 +4799,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B55" s="1">
         <v>16.2</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>128</v>
+      <c r="C55" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>178</v>
+      <c r="E55" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>129</v>
+      <c r="I55" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>29</v>
@@ -5838,26 +4842,8 @@
       <c r="N55" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>29</v>
+      <c r="O55" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V55" s="1" t="s">
         <v>29</v>
@@ -5875,36 +4861,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B56" s="1">
         <v>16.2</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>128</v>
+      <c r="C56" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>179</v>
+      <c r="E56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>129</v>
+      <c r="I56" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>29</v>
@@ -5918,26 +4904,8 @@
       <c r="N56" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>29</v>
+      <c r="O56" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>29</v>
@@ -5955,116 +4923,68 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B57" s="1">
         <v>16.2</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>128</v>
+      <c r="C57" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>180</v>
+      <c r="E57" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z57" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="I57" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B58" s="1">
         <v>16.2</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>128</v>
+      <c r="C58" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>181</v>
+      <c r="E58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>129</v>
+      <c r="I58" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>29</v>
@@ -6078,26 +4998,8 @@
       <c r="N58" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>29</v>
+      <c r="O58" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>29</v>
@@ -6115,36 +5017,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B59" s="1">
         <v>16.2</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>128</v>
+      <c r="C59" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>182</v>
+      <c r="E59" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>129</v>
+      <c r="I59" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>29</v>
@@ -6158,26 +5060,8 @@
       <c r="N59" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U59" s="1" t="s">
-        <v>29</v>
+      <c r="O59" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="V59" s="1" t="s">
         <v>29</v>
@@ -6195,36 +5079,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B60" s="1">
         <v>16.2</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>128</v>
+      <c r="C60" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="E60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>183</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>129</v>
+      <c r="I60" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>29</v>
@@ -6238,26 +5122,8 @@
       <c r="N60" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>29</v>
+      <c r="O60" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>29</v>
@@ -6275,36 +5141,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B61" s="1">
         <v>16.2</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>128</v>
+      <c r="C61" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="E61" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>184</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>129</v>
+      <c r="I61" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>29</v>
@@ -6318,26 +5184,8 @@
       <c r="N61" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>29</v>
+      <c r="O61" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V61" s="1" t="s">
         <v>29</v>
@@ -6355,36 +5203,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B62" s="1">
         <v>16.2</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>128</v>
+      <c r="C62" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F62" s="1" t="s">
+      <c r="E62" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>185</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>129</v>
+      <c r="I62" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>29</v>
@@ -6398,26 +5246,8 @@
       <c r="N62" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U62" s="1" t="s">
-        <v>29</v>
+      <c r="O62" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V62" s="1" t="s">
         <v>29</v>
@@ -6435,36 +5265,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B63" s="1">
         <v>16.2</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>128</v>
+      <c r="C63" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>186</v>
+      <c r="E63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>129</v>
+      <c r="I63" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>29</v>
@@ -6478,26 +5308,8 @@
       <c r="N63" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U63" s="1" t="s">
-        <v>29</v>
+      <c r="O63" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V63" s="1" t="s">
         <v>29</v>
@@ -6515,36 +5327,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B64" s="1">
         <v>16.2</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>128</v>
+      <c r="C64" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>187</v>
+      <c r="E64" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>129</v>
+      <c r="I64" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>29</v>
@@ -6558,26 +5370,8 @@
       <c r="N64" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U64" s="1" t="s">
-        <v>29</v>
+      <c r="O64" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V64" s="1" t="s">
         <v>29</v>
@@ -6595,36 +5389,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B65" s="1">
         <v>16.2</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>128</v>
+      <c r="C65" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>188</v>
+      <c r="E65" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>129</v>
+      <c r="I65" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>29</v>
@@ -6638,26 +5432,8 @@
       <c r="N65" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>29</v>
+      <c r="O65" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V65" s="1" t="s">
         <v>29</v>
@@ -6675,36 +5451,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B66" s="1">
         <v>16.2</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>128</v>
+      <c r="C66" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>189</v>
+      <c r="E66" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>129</v>
+      <c r="I66" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>29</v>
@@ -6718,26 +5494,8 @@
       <c r="N66" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>29</v>
+      <c r="O66" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V66" s="1" t="s">
         <v>29</v>
@@ -6755,36 +5513,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1">
         <v>16.2</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>128</v>
+      <c r="C67" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>138</v>
+      <c r="E67" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>129</v>
+      <c r="I67" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>29</v>
@@ -6798,26 +5556,8 @@
       <c r="N67" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U67" s="1" t="s">
-        <v>29</v>
+      <c r="O67" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V67" s="1" t="s">
         <v>29</v>
@@ -6835,36 +5575,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1">
         <v>16.2</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>128</v>
+      <c r="C68" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>139</v>
+      <c r="E68" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>129</v>
+      <c r="I68" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>29</v>
@@ -6878,26 +5618,8 @@
       <c r="N68" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>29</v>
+      <c r="O68" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V68" s="1" t="s">
         <v>29</v>
@@ -6915,36 +5637,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B69" s="1">
         <v>16.2</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>128</v>
+      <c r="C69" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>140</v>
+      <c r="E69" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>129</v>
+      <c r="I69" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>29</v>
@@ -6958,26 +5680,14 @@
       <c r="N69" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>29</v>
+      <c r="O69" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="V69" s="1" t="s">
         <v>29</v>
@@ -6995,36 +5705,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B70" s="1">
         <v>16.2</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>128</v>
+      <c r="C70" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>141</v>
+      <c r="E70" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>129</v>
+      <c r="I70" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>29</v>
@@ -7038,26 +5748,11 @@
       <c r="N70" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>29</v>
+      <c r="O70" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="V70" s="1" t="s">
         <v>29</v>
@@ -7075,36 +5770,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B71" s="1">
         <v>16.2</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>128</v>
+      <c r="C71" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>142</v>
+      <c r="E71" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>129</v>
+      <c r="I71" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>29</v>
@@ -7118,26 +5813,11 @@
       <c r="N71" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U71" s="1" t="s">
-        <v>29</v>
+      <c r="O71" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="V71" s="1" t="s">
         <v>29</v>
@@ -7155,36 +5835,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B72" s="1">
         <v>16.2</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>128</v>
+      <c r="C72" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>143</v>
+      <c r="E72" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>129</v>
+      <c r="I72" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>29</v>
@@ -7198,26 +5878,8 @@
       <c r="N72" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U72" s="1" t="s">
-        <v>29</v>
+      <c r="O72" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V72" s="1" t="s">
         <v>29</v>
@@ -7235,36 +5897,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B73" s="1">
         <v>16.2</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>128</v>
+      <c r="C73" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>144</v>
+      <c r="E73" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>129</v>
+      <c r="I73" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>29</v>
@@ -7278,26 +5940,20 @@
       <c r="N73" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>29</v>
+      <c r="O73" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="V73" s="1" t="s">
         <v>29</v>
@@ -7315,36 +5971,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1">
         <v>16.2</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>128</v>
+      <c r="C74" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>190</v>
+      <c r="E74" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>129</v>
+      <c r="I74" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>29</v>
@@ -7358,26 +6014,20 @@
       <c r="N74" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U74" s="1" t="s">
-        <v>29</v>
+      <c r="O74" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="V74" s="1" t="s">
         <v>29</v>
@@ -7395,36 +6045,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" ht="33" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1">
         <v>16.2</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>128</v>
+      <c r="C75" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>122</v>
+      <c r="E75" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>129</v>
+      <c r="I75" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>29</v>
@@ -7438,26 +6088,8 @@
       <c r="N75" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U75" s="1" t="s">
-        <v>29</v>
+      <c r="O75" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="V75" s="1" t="s">
         <v>29</v>
@@ -7475,8 +6107,268 @@
         <v>29</v>
       </c>
     </row>
+    <row r="76" spans="1:26" ht="33" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>72</v>
+      </c>
+      <c r="B76" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z76" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" ht="33" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>73</v>
+      </c>
+      <c r="B77" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="V77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z77" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" ht="33" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>74</v>
+      </c>
+      <c r="B78" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z78" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" ht="33" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>75</v>
+      </c>
+      <c r="B79" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="V79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z79" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
